--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487568_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487568_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3737</v>
+        <v>8.2447</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2736</v>
+        <v>6.9041</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1001</v>
+        <v>1.3406</v>
       </c>
       <c r="G2" t="n">
         <v>3.816</v>
@@ -610,13 +610,13 @@
         <v>3.3294</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.713</v>
+        <v>0.1581</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4464</v>
+        <v>0.1841</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2666</v>
+        <v>-0.026</v>
       </c>
       <c r="V2" t="n">
         <v>0.9412</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9342</v>
+        <v>4.7355</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5974</v>
+        <v>4.4521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3368</v>
+        <v>0.2834</v>
       </c>
       <c r="G3" t="n">
         <v>3.7203</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.3885</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9245</v>
+        <v>0.7793</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3374</v>
+        <v>-0.3908</v>
       </c>
       <c r="V3" t="n">
         <v>-1.3318</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2857</v>
+        <v>3.2583</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5021</v>
+        <v>2.8618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7836</v>
+        <v>0.3965</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.9916</v>
+        <v>1.064</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.375</v>
+        <v>-1.9319</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6166</v>
+        <v>2.9959</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0333</v>
+        <v>3.8263</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9833</v>
+        <v>-0.0987</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0501</v>
+        <v>3.9251</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0249</v>
+        <v>-2.7624</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3582</v>
+        <v>-1.8332</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6667</v>
+        <v>-0.9292</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1543</v>
+        <v>3.5253</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5514</v>
+        <v>0.1195</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8973</v>
+        <v>0.2105</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6541</v>
+        <v>-0.091</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5507</v>
+        <v>-0.2754</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2361</v>
+        <v>1.9623</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0266</v>
+        <v>1.183</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2094</v>
+        <v>0.7794</v>
       </c>
       <c r="G5" t="n">
-        <v>1.064</v>
+        <v>0.6845</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9319</v>
+        <v>-0.4512</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9959</v>
+        <v>1.1357</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8263</v>
+        <v>2.7073</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0987</v>
+        <v>1.5872</v>
       </c>
       <c r="L5" t="n">
-        <v>3.9251</v>
+        <v>1.1201</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7624</v>
+        <v>-2.0228</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8332</v>
+        <v>-2.0384</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9292</v>
+        <v>0.0156</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3502</v>
+        <v>0.9792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1751</v>
+        <v>-2.1543</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5253</v>
+        <v>3.1336</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9026999999999999</v>
+        <v>0.0232</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6246</v>
+        <v>0.3546</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2781</v>
+        <v>-0.3314</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>0.2754</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7425</v>
+        <v>1.587</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1236</v>
+        <v>1.2311</v>
       </c>
       <c r="F6" t="n">
-        <v>0.619</v>
+        <v>0.3559</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6845</v>
+        <v>-0.9916</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4512</v>
+        <v>-0.375</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1357</v>
+        <v>-0.6166</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7073</v>
+        <v>1.0333</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5872</v>
+        <v>0.9833</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1201</v>
+        <v>0.0501</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0228</v>
+        <v>-2.0249</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0384</v>
+        <v>-1.3582</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0156</v>
+        <v>-0.6667</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9792</v>
+        <v>1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1336</v>
+        <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1966</v>
+        <v>0.8528</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2952</v>
+        <v>0.6264</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4918</v>
+        <v>0.2264</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0.5507</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.1486</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3045</v>
+        <v>1.0373</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3786</v>
+        <v>0.1113</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0595</v>
@@ -1000,13 +1000,13 @@
         <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5281</v>
+        <v>-0.0626</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9151</v>
+        <v>-0.1823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.387</v>
+        <v>0.1197</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8837</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4927</v>
+        <v>-1.0891</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7068</v>
+        <v>-1.787</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1995</v>
+        <v>0.698</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-2.33</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8864</v>
+        <v>-1.1572</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8943</v>
+        <v>-1.1728</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0004</v>
+        <v>-1.5884</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0415</v>
+        <v>-0.2739</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0412</v>
+        <v>-1.3144</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0083</v>
+        <v>-0.7416</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1551</v>
+        <v>-0.8833</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1468</v>
+        <v>0.1416</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3502</v>
+        <v>1.7626</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5187</v>
+        <v>-0.7971</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3515</v>
+        <v>-0.474</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1672</v>
+        <v>-0.323</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.3745</v>
+        <v>0.2754</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3844</v>
+        <v>-1.5355</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9488</v>
+        <v>-0.0955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5643</v>
+        <v>-1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.33</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1572</v>
+        <v>0.8864</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1728</v>
+        <v>-0.8943</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5884</v>
+        <v>1.0004</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2739</v>
+        <v>2.0415</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3144</v>
+        <v>-1.0412</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7416</v>
+        <v>-1.0083</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8833</v>
+        <v>-1.1551</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1416</v>
+        <v>0.1468</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0925</v>
+        <v>0.4759</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6358</v>
+        <v>0.5493</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4567</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2754</v>
+        <v>-3.3745</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3758</v>
+        <v>-1.7803</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6336</v>
+        <v>-1.188</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2578</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5477</v>
+        <v>-1.9201</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3753</v>
+        <v>-0.7833</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1724</v>
+        <v>-1.1368</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.879</v>
+        <v>-1.1816</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5597</v>
+        <v>-0.5802</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3192</v>
+        <v>-0.6014</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6687</v>
+        <v>-0.7385</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8156</v>
+        <v>-0.2031</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1468</v>
+        <v>-0.5354</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1958</v>
+        <v>1.3709</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0239</v>
+        <v>0.2608</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4205</v>
+        <v>-0.0065</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4445</v>
+        <v>0.2673</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4688</v>
+        <v>-2.5537</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7162</v>
+        <v>-2.8382</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7526</v>
+        <v>0.2845</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9201</v>
+        <v>-2.5477</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7833</v>
+        <v>-1.3753</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1368</v>
+        <v>-1.1724</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1816</v>
+        <v>-1.879</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5802</v>
+        <v>-0.5597</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6014</v>
+        <v>-1.3192</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7385</v>
+        <v>-0.6687</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2031</v>
+        <v>-0.8156</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5354</v>
+        <v>0.1468</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3709</v>
+        <v>0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R11" t="n">
         <v>1.3709</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4277</v>
+        <v>-0.2019</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5346</v>
+        <v>0.2158</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1069</v>
+        <v>-0.4177</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0137</v>
+        <v>-2.6962</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3057</v>
+        <v>-2.0416</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7081</v>
+        <v>-0.6546</v>
       </c>
       <c r="G12" t="n">
         <v>-2.6336</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3802</v>
+        <v>-0.0626</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2794</v>
+        <v>-0.0153</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1008</v>
+        <v>-0.0473</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1149</v>
+        <v>-2.9858</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3855</v>
+        <v>-2.2831</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7294</v>
+        <v>-0.7027</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6999</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1604</v>
+        <v>-0.0313</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0418</v>
+        <v>0.0606</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1186</v>
+        <v>-0.0919</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2754</v>
@@ -1501,28 +1501,28 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.404899999999998</v>
+        <v>8.295800000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5448</v>
+        <v>7.435999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.8601000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9055</v>
+        <v>-2.905499999999998</v>
       </c>
       <c r="H14" t="n">
         <v>-6.8171</v>
       </c>
       <c r="I14" t="n">
-        <v>3.911799999999999</v>
+        <v>3.911800000000001</v>
       </c>
       <c r="J14" t="n">
         <v>13.2552</v>
       </c>
       <c r="K14" t="n">
-        <v>6.770499999999999</v>
+        <v>6.7705</v>
       </c>
       <c r="L14" t="n">
         <v>6.484900000000001</v>
@@ -1540,19 +1540,19 @@
         <v>15.6677</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.833700000000001</v>
+        <v>-7.833699999999999</v>
       </c>
       <c r="R14" t="n">
         <v>23.5017</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2322000000000002</v>
+        <v>1.1233</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4113</v>
+        <v>2.3025</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1793</v>
+        <v>-1.1791</v>
       </c>
       <c r="V14" t="n">
         <v>-5.590100000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.3021</v>
+        <v>4.6283</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8735</v>
+        <v>4.4641</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4286</v>
+        <v>0.1641</v>
       </c>
       <c r="G15" t="n">
         <v>3.8832</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2771</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7111</v>
+        <v>0.3017</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5661</v>
+        <v>0.3016</v>
       </c>
       <c r="V15" t="n">
         <v>2.1003</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.329</v>
+        <v>3.1096</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0121</v>
+        <v>1.6027</v>
       </c>
       <c r="F16" t="n">
-        <v>1.317</v>
+        <v>1.5069</v>
       </c>
       <c r="G16" t="n">
         <v>1.8642</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4867</v>
+        <v>0.2673</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5634</v>
+        <v>0.1541</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0767</v>
+        <v>0.1132</v>
       </c>
       <c r="V16" t="n">
         <v>0.3905</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9881</v>
+        <v>1.1734</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7402</v>
+        <v>-0.6379</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7283</v>
+        <v>1.8113</v>
       </c>
       <c r="G17" t="n">
         <v>0.0608</v>
@@ -1780,13 +1780,13 @@
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1303</v>
+        <v>0.055</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0115</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.6659</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.093</v>
+        <v>-0.4863</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0695</v>
+        <v>2.3765</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.1625</v>
+        <v>-2.8629</v>
       </c>
       <c r="G18" t="n">
         <v>0.5829</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7173</v>
+        <v>-0.1107</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1317</v>
+        <v>0.1753</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5856</v>
+        <v>-0.286</v>
       </c>
       <c r="V18" t="n">
         <v>0.6083</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. GRANJA I BERNAD</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6517</v>
+        <v>-0.9386</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.4186</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2762</v>
+        <v>-1.3572</v>
       </c>
       <c r="G19" t="n">
-        <v>3.0282</v>
+        <v>-0.2632</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2856</v>
+        <v>0.6252</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2573</v>
+        <v>-0.8884</v>
       </c>
       <c r="J19" t="n">
-        <v>5.5553</v>
+        <v>2.468</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3688</v>
+        <v>1.7761</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1865</v>
+        <v>0.6919</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5271</v>
+        <v>-2.7312</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0833</v>
+        <v>-1.151</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4438</v>
+        <v>-1.5803</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.7004</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.8755</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2549</v>
+        <v>-0.2664</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6693</v>
+        <v>0.0047</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9242</v>
+        <v>-0.2711</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2754</v>
+        <v>1.5495</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8937</v>
+        <v>-1.3278</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4001</v>
+        <v>-0.6441</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4937</v>
+        <v>-0.6837</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2632</v>
+        <v>-0.1632</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6252</v>
+        <v>0.1902</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8884</v>
+        <v>-0.3534</v>
       </c>
       <c r="J20" t="n">
-        <v>2.468</v>
+        <v>0.7056</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7761</v>
+        <v>0.6652</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6919</v>
+        <v>0.0404</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7312</v>
+        <v>-0.8687</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.151</v>
+        <v>-0.475</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5803</v>
+        <v>-0.3938</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.5668</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.9585</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.9377</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2216</v>
+        <v>0.4021</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.3335</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4076</v>
+        <v>0.0687</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8837</v>
+        <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6659</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>I. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0027</v>
+        <v>-1.7061</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1558</v>
+        <v>0.1128</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8469</v>
+        <v>-1.819</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1632</v>
+        <v>3.0282</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1902</v>
+        <v>3.2856</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3534</v>
+        <v>-0.2573</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7056</v>
+        <v>5.5553</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6652</v>
+        <v>4.3688</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0404</v>
+        <v>1.1865</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8687</v>
+        <v>-2.5271</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.475</v>
+        <v>-1.0833</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3938</v>
+        <v>-1.4438</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5668</v>
+        <v>-4.7004</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9585</v>
+        <v>-5.8755</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2727</v>
+        <v>-0.3094</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1782</v>
+        <v>0.1576</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0945</v>
+        <v>-0.467</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="W21" t="n">
         <v>0.2754</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0204</v>
+        <v>-1.8646</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6543</v>
+        <v>-3.5519</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6338</v>
+        <v>1.6873</v>
       </c>
       <c r="G22" t="n">
         <v>0.347</v>
@@ -2170,13 +2170,13 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1786</v>
+        <v>0.3344</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2376</v>
+        <v>-0.1353</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4162</v>
+        <v>0.4696</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1888</v>
+        <v>-2.4617</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3186</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5074</v>
+        <v>-2.371</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7377</v>
@@ -2248,13 +2248,13 @@
         <v>0.5875</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9198</v>
+        <v>0.6469</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7881</v>
+        <v>0.3788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1317</v>
+        <v>0.2682</v>
       </c>
       <c r="V23" t="n">
         <v>-0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.1738</v>
+        <v>-6.1665</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.8079</v>
+        <v>-4.9102</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.366</v>
+        <v>-1.2562</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6969</v>
@@ -2326,13 +2326,13 @@
         <v>0.9792</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4977</v>
+        <v>-0.4904</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0723</v>
+        <v>-0.1747</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4254</v>
+        <v>-0.3157</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4049</v>
+        <v>-6.040299999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8601000000000001</v>
+        <v>-0.860199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.545</v>
+        <v>-5.1804</v>
       </c>
       <c r="G25" t="n">
         <v>2.9053</v>
@@ -2404,13 +2404,13 @@
         <v>7.833699999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2323000000000005</v>
+        <v>1.1321</v>
       </c>
       <c r="T25" t="n">
-        <v>1.1793</v>
+        <v>1.1792</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.4115</v>
+        <v>-0.04700000000000004</v>
       </c>
       <c r="V25" t="n">
         <v>5.5899</v>
